--- a/verificables revisión sistemática/S16_excluidos_en_la_fase_de_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_en_la_fase_de_texto_completo.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>Los estudios que el cribado admitió y que salieron después, en la fase de texto completo: uno por fila, con su código de motivo y lo que significa, la cita en que se apoya cuando la hay, quién decidió la exclusión y cuándo. El modelo de lenguaje leyó los textos completos y las fichas de registro y propuso, con su cita, las exclusiones que se apoyan en los textos que leyó. En «Quién decidió», 89 llevan la firma de los dos autores, 2 la de D.V. solo y 27 se registraron por orden de D.V., sin que conste la firma de N.T. Los NOPDF salieron por no tener el artículo completo, no porque se comprobara que incumplen los criterios; ni ellos ni los NOREC tienen nada que citar, y 4 más van sin cita. De las que llevan cita, 17 citan la ficha del registro y 1, la indexación de SciELO.</t>
         </is>
       </c>
     </row>
@@ -514,140 +521,151 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sección 3.1.1 y Figura 1 (PRISMA 2020, ítem 16b).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>118 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>codigo</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Código del motivo</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: codigo</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>que_significa_el_codigo</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Qué significa el código</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: que_significa_el_codigo</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>motivo</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: motivo</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>cita_del_texto</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Cita en que se apoya</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: cita_del_texto</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: titulo</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>decidido_por</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Quién decidió</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: decidido_por</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: fecha</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Generado el 2026-10-19</t>
         </is>
@@ -670,50 +688,50 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>codigo</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>que_significa_el_codigo</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>motivo</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>cita_del_texto</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Código del motivo</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Qué significa el código</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Cita en que se apoya</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>decidido_por</t>
-        </is>
-      </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Quién decidió</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
@@ -732,7 +750,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11)</t>
+          <t>Informe no redactado en inglés ni en español (criterio de idioma, enmienda 2026-08-11)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -774,7 +792,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11)</t>
+          <t>Informe no redactado en inglés ni en español (criterio de idioma, enmienda 2026-08-11)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -816,7 +834,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11)</t>
+          <t>Informe no redactado en inglés ni en español (criterio de idioma, enmienda 2026-08-11)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -858,7 +876,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11)</t>
+          <t>Informe no redactado en inglés ni en español (criterio de idioma, enmienda 2026-08-11)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -900,7 +918,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>La intervencion no es un bacteriofago (endolisina u otro derivado)</t>
+          <t>La intervención no es un bacteriófago (endolisina u otro derivado)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -942,7 +960,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La intervencion no es un bacteriofago (endolisina u otro derivado)</t>
+          <t>La intervención no es un bacteriófago (endolisina u otro derivado)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -984,7 +1002,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
+          <t>Trabajo de laboratorio, preclínico o de modelización; sin pacientes tratados</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1026,7 +1044,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
+          <t>Trabajo de laboratorio, preclínico o de modelización; sin pacientes tratados</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1068,7 +1086,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
+          <t>Trabajo de laboratorio, preclínico o de modelización; sin pacientes tratados</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1110,7 +1128,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Texto completo no recuperado: no se pudo verificar contra el articulo</t>
+          <t>Texto completo no recuperado: no se pudo verificar contra el artículo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1152,7 +1170,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+          <t>No evalúa fagoterapia en pacientes (encuesta, epidemiología, prensa, otra terapia)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1194,7 +1212,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+          <t>No evalúa fagoterapia en pacientes (encuesta, epidemiología, prensa, otra terapia)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1682,7 +1700,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Protocolo de estudio: declara lo que se hará, sin resultados</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1724,7 +1742,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Protocolo de estudio: declara lo que se hará, sin resultados</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1766,7 +1784,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Protocolo de estudio: declara lo que se hará, sin resultados</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1808,7 +1826,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Protocolo de estudio: declara lo que se hará, sin resultados</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1850,7 +1868,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Revision narrativa o comentario, sin datos primarios propios</t>
+          <t>Revisión narrativa o comentario, sin datos primarios propios</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1892,7 +1910,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Revision narrativa o comentario, sin datos primarios propios</t>
+          <t>Revisión narrativa o comentario, sin datos primarios propios</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2186,7 +2204,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+          <t>No evalúa fagoterapia en pacientes (encuesta, epidemiología, prensa, otra terapia)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2228,7 +2246,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+          <t>No evalúa fagoterapia en pacientes (encuesta, epidemiología, prensa, otra terapia)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2354,7 +2372,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+          <t>La ficha de registro no declara ningún organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2396,7 +2414,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+          <t>La ficha de registro no declara ningún organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2438,7 +2456,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+          <t>La ficha de registro no declara ningún organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2480,7 +2498,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+          <t>La ficha de registro no declara ningún organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2522,7 +2540,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+          <t>La ficha de registro no declara ningún organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2564,7 +2582,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+          <t>La ficha de registro no declara ningún organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2606,7 +2624,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+          <t>La ficha de registro no declara ningún organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2648,7 +2666,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Protocolo de estudio: declara lo que se hará, sin resultados</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2900,7 +2918,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Texto completo no recuperado: no se pudo verificar contra el articulo</t>
+          <t>Texto completo no recuperado: no se pudo verificar contra el artículo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2942,7 +2960,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Texto completo no recuperado: no se pudo verificar contra el articulo</t>
+          <t>Texto completo no recuperado: no se pudo verificar contra el artículo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2984,7 +3002,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Texto completo no recuperado: no se pudo verificar contra el articulo</t>
+          <t>Texto completo no recuperado: no se pudo verificar contra el artículo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3026,7 +3044,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3068,7 +3086,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3110,7 +3128,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3152,7 +3170,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3194,7 +3212,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3236,7 +3254,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3278,7 +3296,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3320,7 +3338,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3362,7 +3380,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3404,7 +3422,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3446,7 +3464,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3488,7 +3506,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3530,7 +3548,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3572,7 +3590,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3614,7 +3632,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3656,7 +3674,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3698,7 +3716,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3740,7 +3758,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3782,7 +3800,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3824,7 +3842,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3866,7 +3884,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3908,7 +3926,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3950,7 +3968,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3992,7 +4010,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4034,7 +4052,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4076,7 +4094,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4118,7 +4136,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4160,7 +4178,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4202,7 +4220,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4244,7 +4262,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4286,7 +4304,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4328,7 +4346,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4370,7 +4388,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4412,7 +4430,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4454,7 +4472,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4496,7 +4514,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4538,7 +4556,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4580,7 +4598,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4622,7 +4640,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4664,7 +4682,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4706,7 +4724,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4748,7 +4766,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4790,7 +4808,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4832,7 +4850,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4874,7 +4892,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4916,7 +4934,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4958,7 +4976,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5000,7 +5018,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5042,7 +5060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5084,7 +5102,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5126,7 +5144,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5168,7 +5186,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5210,7 +5228,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5252,7 +5270,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5294,7 +5312,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5336,7 +5354,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5378,7 +5396,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5420,7 +5438,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5462,7 +5480,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5504,7 +5522,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5546,7 +5564,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5588,7 +5606,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5630,7 +5648,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+          <t>Sin PDF del artículo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">

--- a/verificables revisión sistemática/S16_excluidos_en_la_fase_de_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_en_la_fase_de_texto_completo.xlsx
@@ -667,7 +667,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
